--- a/data/trans_orig/CoPsoQ-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/CoPsoQ-Provincia-trans_orig.xlsx
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>41343</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61797</t>
+          <t>63404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25890</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44500</t>
+          <t>45176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70884</t>
+          <t>71920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100058</t>
+          <t>102594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,79%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17100</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35464</t>
+          <t>35574</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25448</t>
+          <t>25310</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31465</t>
+          <t>31760</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56041</t>
+          <t>56444</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35098</t>
+          <t>34865</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57797</t>
+          <t>57350</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24248</t>
+          <t>23216</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42476</t>
+          <t>42812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63162</t>
+          <t>63687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93150</t>
+          <t>91791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,55%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92295</t>
+          <t>91397</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118237</t>
+          <t>118100</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57086</t>
+          <t>57250</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80554</t>
+          <t>81094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158323</t>
+          <t>156175</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192704</t>
+          <t>191492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19377</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41218</t>
+          <t>42839</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15510</t>
+          <t>16299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34763</t>
+          <t>35701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41259</t>
+          <t>41805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69226</t>
+          <t>69346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25209</t>
+          <t>25615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48406</t>
+          <t>47984</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>17796</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38003</t>
+          <t>36077</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47613</t>
+          <t>49013</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76438</t>
+          <t>77520</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65520</t>
+          <t>64126</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>87842</t>
+          <t>86478</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>39468</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>92122</t>
+          <t>91764</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>120874</t>
+          <t>121699</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,22%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19626</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>37872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33935</t>
+          <t>33444</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40364</t>
+          <t>41659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66286</t>
+          <t>66214</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>21151</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41603</t>
+          <t>41347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15439</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30851</t>
+          <t>32544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40645</t>
+          <t>41557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65413</t>
+          <t>67154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67005</t>
+          <t>67338</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91941</t>
+          <t>91734</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40040</t>
+          <t>39950</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60296</t>
+          <t>60017</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>114123</t>
+          <t>114373</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146903</t>
+          <t>147020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,76%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>24502</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>45137</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25232</t>
+          <t>25540</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>45066</t>
+          <t>44678</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>54575</t>
+          <t>53912</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>83618</t>
+          <t>83318</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18253</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38938</t>
+          <t>39138</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22908</t>
+          <t>24642</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31454</t>
+          <t>30255</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57113</t>
+          <t>55133</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>19233</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37352</t>
+          <t>37710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>18078</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32197</t>
+          <t>32524</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41762</t>
+          <t>41377</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64976</t>
+          <t>65349</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,08%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21696</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22296</t>
+          <t>21139</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>20130</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39889</t>
+          <t>41048</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>29752</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>48927</t>
+          <t>48170</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21866</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>41803</t>
+          <t>43010</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>65909</t>
+          <t>66689</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>55656</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>78242</t>
+          <t>77075</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31185</t>
+          <t>30870</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>75130</t>
+          <t>76833</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>102458</t>
+          <t>104392</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>61,46%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15607</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>36478</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22534</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>28654</t>
+          <t>28219</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>51363</t>
+          <t>50971</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32483</t>
+          <t>32762</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11324</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>25656</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>30351</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>54465</t>
+          <t>54665</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>126986</t>
+          <t>128847</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>162585</t>
+          <t>161760</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>66587</t>
+          <t>65858</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>93912</t>
+          <t>93407</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>205767</t>
+          <t>205122</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>250077</t>
+          <t>247836</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,45%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>40496</t>
+          <t>39956</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>69484</t>
+          <t>68134</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>33043</t>
+          <t>33953</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>57526</t>
+          <t>58282</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>81791</t>
+          <t>81104</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>121609</t>
+          <t>120508</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>52437</t>
+          <t>54133</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>83312</t>
+          <t>84891</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>42760</t>
+          <t>42805</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>67599</t>
+          <t>68086</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>102992</t>
+          <t>102844</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>141725</t>
+          <t>141745</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>238906</t>
+          <t>238854</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>273911</t>
+          <t>272153</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>173674</t>
+          <t>172613</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>201794</t>
+          <t>203085</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>423221</t>
+          <t>425459</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>468586</t>
+          <t>470227</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>44578</t>
+          <t>44306</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>72687</t>
+          <t>72049</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>21847</t>
+          <t>21853</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>44655</t>
+          <t>44479</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>73556</t>
+          <t>71728</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>108889</t>
+          <t>109765</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>33360</t>
+          <t>34595</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>61017</t>
+          <t>61296</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>24596</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>47648</t>
+          <t>49181</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>62748</t>
+          <t>63481</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>98291</t>
+          <t>98154</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>774730</t>
+          <t>767735</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>848278</t>
+          <t>844525</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>469687</t>
+          <t>470536</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>534587</t>
+          <t>534354</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1269457</t>
+          <t>1265943</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1370213</t>
+          <t>1364162</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>240014</t>
+          <t>238459</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>300717</t>
+          <t>300433</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>181284</t>
+          <t>183497</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>232626</t>
+          <t>235905</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>432411</t>
+          <t>434119</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>513223</t>
+          <t>513624</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>280709</t>
+          <t>284308</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>345507</t>
+          <t>350478</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>195098</t>
+          <t>191829</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>245692</t>
+          <t>245807</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>490640</t>
+          <t>490964</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>576318</t>
+          <t>571919</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37806</t>
+          <t>37643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60953</t>
+          <t>61235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33034</t>
+          <t>33654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52325</t>
+          <t>53075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76336</t>
+          <t>77267</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109210</t>
+          <t>110050</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,41%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29837</t>
+          <t>29561</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52938</t>
+          <t>52783</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36364</t>
+          <t>36298</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52418</t>
+          <t>53217</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>82976</t>
+          <t>82695</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34829</t>
+          <t>35626</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58405</t>
+          <t>60234</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23372</t>
+          <t>22121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41877</t>
+          <t>40375</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62591</t>
+          <t>62890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92429</t>
+          <t>93963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -6771,12 +6771,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76148</t>
+          <t>75883</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101146</t>
+          <t>103029</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58055</t>
+          <t>56240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78320</t>
+          <t>77684</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6841,12 +6841,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140634</t>
+          <t>139645</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175296</t>
+          <t>174990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6856,12 +6856,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,62%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32008</t>
+          <t>32900</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55530</t>
+          <t>58070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30311</t>
+          <t>31581</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49441</t>
+          <t>51894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78661</t>
+          <t>80659</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28455</t>
+          <t>27212</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49311</t>
+          <t>48288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>16111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33084</t>
+          <t>33892</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49249</t>
+          <t>48365</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>76482</t>
+          <t>77007</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -7340,12 +7340,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43312</t>
+          <t>42808</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65118</t>
+          <t>64991</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24952</t>
+          <t>26367</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42716</t>
+          <t>44712</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>74067</t>
+          <t>74699</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>103338</t>
+          <t>102127</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25459</t>
+          <t>25672</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44894</t>
+          <t>45747</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>36378</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51093</t>
+          <t>50962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77103</t>
+          <t>75139</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28017</t>
+          <t>28659</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48392</t>
+          <t>48225</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>15037</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31186</t>
+          <t>30256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46912</t>
+          <t>48398</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71847</t>
+          <t>73396</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39843</t>
+          <t>39567</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62450</t>
+          <t>60956</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25829</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43730</t>
+          <t>43744</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71643</t>
+          <t>71202</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101467</t>
+          <t>99822</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>51,44%</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8022,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36702</t>
+          <t>36636</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22384</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8072,12 +8072,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>31616</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54033</t>
+          <t>54166</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8107,12 +8107,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>24957</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45601</t>
+          <t>45271</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23164</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41529</t>
+          <t>41682</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8185,12 +8185,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53116</t>
+          <t>53460</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81772</t>
+          <t>81276</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8220,12 +8220,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,89%</t>
         </is>
       </c>
     </row>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41780</t>
+          <t>40795</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59165</t>
+          <t>58446</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25468</t>
+          <t>24699</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39691</t>
+          <t>39028</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70961</t>
+          <t>71593</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93150</t>
+          <t>93670</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,7%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25731</t>
+          <t>26402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22776</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42059</t>
+          <t>41510</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8676,12 +8676,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -8704,12 +8704,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20331</t>
+          <t>19443</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8719,12 +8719,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>31441</t>
+          <t>31836</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -9047,12 +9047,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47669</t>
+          <t>46934</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>68935</t>
+          <t>68274</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -9062,12 +9062,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>35912</t>
+          <t>35598</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52999</t>
+          <t>52177</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -9097,12 +9097,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>88785</t>
+          <t>88614</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>116038</t>
+          <t>115225</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>62,94%</t>
         </is>
       </c>
     </row>
@@ -9160,12 +9160,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19180</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>38488</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9175,12 +9175,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>31648</t>
+          <t>29986</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>38085</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>62482</t>
+          <t>64411</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -9245,12 +9245,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -9273,12 +9273,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13956</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>31281</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -9288,12 +9288,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>14487</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20341</t>
+          <t>20644</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>41682</t>
+          <t>42113</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9358,12 +9358,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -9616,12 +9616,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>145372</t>
+          <t>147192</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>187730</t>
+          <t>187382</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>121167</t>
+          <t>122308</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>156654</t>
+          <t>156020</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9686,12 +9686,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>278892</t>
+          <t>275576</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>333057</t>
+          <t>332035</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,49%</t>
         </is>
       </c>
     </row>
@@ -9729,12 +9729,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>68195</t>
+          <t>68459</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>103584</t>
+          <t>103108</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9764,12 +9764,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>49365</t>
+          <t>49586</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>78766</t>
+          <t>76948</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>125787</t>
+          <t>127122</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>170634</t>
+          <t>173512</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>88652</t>
+          <t>88714</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>127360</t>
+          <t>126232</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>68054</t>
+          <t>68899</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>98940</t>
+          <t>98998</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>166053</t>
+          <t>164649</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>215380</t>
+          <t>214045</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -10185,12 +10185,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>246895</t>
+          <t>245562</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>275996</t>
+          <t>275864</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>162025</t>
+          <t>160741</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>189895</t>
+          <t>188935</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>416597</t>
+          <t>417627</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>457376</t>
+          <t>457735</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,39%</t>
         </is>
       </c>
     </row>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>32854</t>
+          <t>33722</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>58825</t>
+          <t>60510</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>25430</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>47204</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>64893</t>
+          <t>65449</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>98735</t>
+          <t>99469</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -10411,12 +10411,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>32184</t>
+          <t>31047</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>20140</t>
+          <t>20330</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>40762</t>
+          <t>41311</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>37153</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>65702</t>
+          <t>66245</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10496,12 +10496,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>745027</t>
+          <t>741230</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>821252</t>
+          <t>819477</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -10789,12 +10789,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>540769</t>
+          <t>540879</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>602641</t>
+          <t>604002</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1300916</t>
+          <t>1304801</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1401649</t>
+          <t>1404483</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -10839,12 +10839,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>289544</t>
+          <t>287833</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>353561</t>
+          <t>355907</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>199765</t>
+          <t>201273</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>254134</t>
+          <t>251522</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -10917,12 +10917,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -10937,12 +10937,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>504803</t>
+          <t>508623</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>589018</t>
+          <t>593410</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -10952,12 +10952,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -10980,12 +10980,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>288229</t>
+          <t>289109</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>353114</t>
+          <t>353064</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>214666</t>
+          <t>213218</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>268141</t>
+          <t>270388</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>519414</t>
+          <t>519396</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>603912</t>
+          <t>602496</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -11441,32 +11441,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>243654</t>
+          <t>254982</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>224026</t>
+          <t>241195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>256014</t>
+          <t>265453</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11476,32 +11476,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>235525</t>
+          <t>257445</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>226000</t>
+          <t>248399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>243494</t>
+          <t>266146</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11511,32 +11511,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>479179</t>
+          <t>512428</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>458569</t>
+          <t>496376</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>493979</t>
+          <t>526562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -11554,32 +11554,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16349</t>
+          <t>17277</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>27415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11589,32 +11589,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>16372</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>24196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11624,32 +11624,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32720</t>
+          <t>33649</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>24091</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43663</t>
+          <t>45043</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -11667,32 +11667,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17606</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10445</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>26839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11702,32 +11702,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12497</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19022</t>
+          <t>20341</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11737,32 +11737,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30103</t>
+          <t>31791</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21019</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42944</t>
+          <t>42366</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -11780,32 +11780,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32783</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11815,32 +11815,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11850,32 +11850,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>20001</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -11893,17 +11893,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>286456</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>286456</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>286456</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11928,17 +11928,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>267645</t>
+          <t>290688</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>267645</t>
+          <t>290688</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>267645</t>
+          <t>290688</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11963,17 +11963,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>554101</t>
+          <t>587323</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>554101</t>
+          <t>587323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>554101</t>
+          <t>587323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12010,32 +12010,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>403331</t>
+          <t>408392</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>383391</t>
+          <t>390108</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>416904</t>
+          <t>422459</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12045,32 +12045,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>377696</t>
+          <t>397356</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>365218</t>
+          <t>384114</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>388235</t>
+          <t>407478</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12080,32 +12080,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>781027</t>
+          <t>805748</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>759956</t>
+          <t>783952</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>799596</t>
+          <t>825129</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -12123,32 +12123,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12158,32 +12158,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20146</t>
+          <t>20401</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12614</t>
+          <t>13260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29315</t>
+          <t>29740</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12193,32 +12193,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>30205</t>
+          <t>34139</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43023</t>
+          <t>47130</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -12236,32 +12236,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>14880</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27721</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12271,32 +12271,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13651</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12306,32 +12306,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>23060</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>13936</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36011</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -12349,32 +12349,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36325</t>
+          <t>37257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12384,32 +12384,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>16254</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21251</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12419,32 +12419,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>35299</t>
+          <t>39427</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>28152</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>55343</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -12462,17 +12462,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>449099</t>
+          <t>460183</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>449099</t>
+          <t>460183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>449099</t>
+          <t>460183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12497,17 +12497,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>419451</t>
+          <t>442190</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>419451</t>
+          <t>442190</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>419451</t>
+          <t>442190</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12532,17 +12532,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>868550</t>
+          <t>902373</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>868550</t>
+          <t>902373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>868550</t>
+          <t>902373</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12579,32 +12579,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>261813</t>
+          <t>263355</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>249209</t>
+          <t>251865</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271993</t>
+          <t>272041</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12614,32 +12614,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>265901</t>
+          <t>271886</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>257610</t>
+          <t>262893</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274240</t>
+          <t>280013</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12649,32 +12649,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>527714</t>
+          <t>535242</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>513113</t>
+          <t>519753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>540297</t>
+          <t>546506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -12692,32 +12692,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>14467</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12727,32 +12727,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11186</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17066</t>
+          <t>18290</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12762,32 +12762,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>27238</t>
+          <t>28608</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -12805,32 +12805,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15463</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12840,32 +12840,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8971</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14745</t>
+          <t>14709</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12875,32 +12875,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24425</t>
+          <t>23927</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35660</t>
+          <t>35654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -12918,22 +12918,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15519</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12953,32 +12953,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12988,32 +12988,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>15347</t>
+          <t>14863</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9147</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24264</t>
+          <t>23380</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -13031,17 +13031,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>292188</t>
+          <t>292815</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>292188</t>
+          <t>292815</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>292188</t>
+          <t>292815</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13066,17 +13066,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>293789</t>
+          <t>300305</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>293789</t>
+          <t>300305</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>293789</t>
+          <t>300305</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13101,17 +13101,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>585977</t>
+          <t>593120</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>585977</t>
+          <t>593120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>585977</t>
+          <t>593120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13148,32 +13148,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>239532</t>
+          <t>281387</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>221162</t>
+          <t>256695</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>254994</t>
+          <t>300904</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13183,32 +13183,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>395540</t>
+          <t>330467</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>377283</t>
+          <t>314648</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>412594</t>
+          <t>342254</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13218,32 +13218,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>635072</t>
+          <t>611854</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>602948</t>
+          <t>583521</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>662441</t>
+          <t>634543</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -13261,32 +13261,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>22105</t>
+          <t>25001</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11265</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38132</t>
+          <t>46876</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13296,32 +13296,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15574</t>
+          <t>17983</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29942</t>
+          <t>30150</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13331,32 +13331,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>37680</t>
+          <t>42984</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24555</t>
+          <t>27747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60864</t>
+          <t>67008</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -13374,32 +13374,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>19542</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32343</t>
+          <t>35290</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13409,32 +13409,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12184</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13444,32 +13444,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>22679</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>16776</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>37722</t>
+          <t>43203</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -13487,32 +13487,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>24260</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>13627</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26526</t>
+          <t>43217</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13522,32 +13522,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17719</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>29598</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13557,32 +13557,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>32806</t>
+          <t>43738</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>29897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49747</t>
+          <t>63491</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -13600,17 +13600,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>293115</t>
+          <t>350190</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>293115</t>
+          <t>350190</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>293115</t>
+          <t>350190</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>435122</t>
+          <t>376434</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>435122</t>
+          <t>376434</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>435122</t>
+          <t>376434</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13670,17 +13670,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>728237</t>
+          <t>726624</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>728237</t>
+          <t>726624</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>728237</t>
+          <t>726624</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13717,32 +13717,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>150718</t>
+          <t>174216</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>141980</t>
+          <t>165477</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>157600</t>
+          <t>181575</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13752,32 +13752,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>168621</t>
+          <t>184534</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>161087</t>
+          <t>176204</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174679</t>
+          <t>190332</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13787,32 +13787,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>319340</t>
+          <t>358750</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>308126</t>
+          <t>346481</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>328578</t>
+          <t>368429</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -13830,32 +13830,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13662</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13865,32 +13865,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>8031</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13900,22 +13900,22 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -13943,32 +13943,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13978,32 +13978,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>19197</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14013,32 +14013,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>18079</t>
+          <t>19424</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12026</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26558</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -14056,32 +14056,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14091,32 +14091,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13474</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14126,32 +14126,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>14255</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19170</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -14169,17 +14169,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>170916</t>
+          <t>196948</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>170916</t>
+          <t>196948</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>170916</t>
+          <t>196948</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14204,17 +14204,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>189756</t>
+          <t>207799</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>189756</t>
+          <t>207799</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>189756</t>
+          <t>207799</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>360672</t>
+          <t>404747</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>360672</t>
+          <t>404747</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>360672</t>
+          <t>404747</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14286,32 +14286,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>210613</t>
+          <t>209357</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>200658</t>
+          <t>198660</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>220366</t>
+          <t>217970</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14321,32 +14321,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>193994</t>
+          <t>199064</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>185217</t>
+          <t>190777</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>199728</t>
+          <t>204861</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14356,32 +14356,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>404608</t>
+          <t>408421</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>391811</t>
+          <t>394072</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>417140</t>
+          <t>419213</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -14399,32 +14399,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>15826</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>24986</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14434,32 +14434,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17688</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14469,32 +14469,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>26390</t>
+          <t>26989</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>18290</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>37359</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -14512,32 +14512,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14547,32 +14547,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>9884</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14582,32 +14582,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>10246</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>17579</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -14625,32 +14625,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18542</t>
+          <t>20533</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14660,32 +14660,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2183</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14695,32 +14695,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25269</t>
+          <t>25660</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -14738,17 +14738,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>242876</t>
+          <t>243824</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>242876</t>
+          <t>243824</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>242876</t>
+          <t>243824</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14773,17 +14773,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>214676</t>
+          <t>219792</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>214676</t>
+          <t>219792</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>214676</t>
+          <t>219792</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -14808,17 +14808,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>457553</t>
+          <t>463616</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>457553</t>
+          <t>463616</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>457553</t>
+          <t>463616</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -14855,32 +14855,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>454613</t>
+          <t>528075</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>433009</t>
+          <t>508407</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>471206</t>
+          <t>546727</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14890,32 +14890,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>671798</t>
+          <t>567453</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>632961</t>
+          <t>550583</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>716078</t>
+          <t>583157</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14925,32 +14925,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1126412</t>
+          <t>1095527</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1083377</t>
+          <t>1067763</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1192073</t>
+          <t>1117873</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>87,3%</t>
         </is>
       </c>
     </row>
@@ -14968,17 +14968,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>32459</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>47398</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -15003,32 +15003,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>35480</t>
+          <t>43437</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>32724</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>53508</t>
+          <t>56325</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -15038,32 +15038,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>63510</t>
+          <t>75896</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>38545</t>
+          <t>59851</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>85870</t>
+          <t>93090</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -15081,32 +15081,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>19378</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>12501</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>30567</t>
+          <t>32888</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -15116,32 +15116,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>15232</t>
+          <t>17575</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>11582</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>26639</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -15151,32 +15151,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>34610</t>
+          <t>38599</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>19941</t>
+          <t>28668</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>49040</t>
+          <t>52268</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -15194,32 +15194,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>33135</t>
+          <t>37634</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>26105</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>47967</t>
+          <t>53299</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -15229,32 +15229,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>32892</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>48468</t>
+          <t>45217</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -15264,32 +15264,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>63792</t>
+          <t>70525</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>37870</t>
+          <t>55169</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>84949</t>
+          <t>89644</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -15307,17 +15307,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>535156</t>
+          <t>619191</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>535156</t>
+          <t>619191</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>535156</t>
+          <t>619191</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -15342,17 +15342,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>753167</t>
+          <t>661357</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>753167</t>
+          <t>661357</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>753167</t>
+          <t>661357</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -15377,17 +15377,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1288323</t>
+          <t>1280548</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1288323</t>
+          <t>1280548</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1288323</t>
+          <t>1280548</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -15424,32 +15424,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>469347</t>
+          <t>553118</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>186002</t>
+          <t>527158</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>672276</t>
+          <t>574476</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -15459,32 +15459,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>497269</t>
+          <t>573860</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>480802</t>
+          <t>556441</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>511424</t>
+          <t>589186</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -15494,32 +15494,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>966616</t>
+          <t>1126978</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>560509</t>
+          <t>1098575</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1177968</t>
+          <t>1154761</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -15537,32 +15537,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>59839</t>
+          <t>68597</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>22881</t>
+          <t>54634</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>92149</t>
+          <t>86909</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -15572,27 +15572,27 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>53465</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>41509</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>58110</t>
+          <t>67185</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -15607,32 +15607,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>106467</t>
+          <t>122062</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>102087</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>136880</t>
+          <t>144439</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -15650,32 +15650,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>24952</t>
+          <t>28652</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>18271</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>40543</t>
+          <t>42632</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -15685,32 +15685,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>21490</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>26626</t>
+          <t>31244</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15720,32 +15720,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>42684</t>
+          <t>50142</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>23616</t>
+          <t>36775</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>59945</t>
+          <t>65468</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -15763,32 +15763,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>278505</t>
+          <t>39646</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>43264</t>
+          <t>26529</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>611843</t>
+          <t>54361</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15798,32 +15798,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>25005</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>14367</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>29853</t>
+          <t>35265</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15833,32 +15833,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>299499</t>
+          <t>64651</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>49812</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>759831</t>
+          <t>81199</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -15876,17 +15876,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>832642</t>
+          <t>690013</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>832642</t>
+          <t>690013</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>832642</t>
+          <t>690013</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15911,17 +15911,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>582624</t>
+          <t>673820</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>582624</t>
+          <t>673820</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>582624</t>
+          <t>673820</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15946,17 +15946,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1415266</t>
+          <t>1363833</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1415266</t>
+          <t>1363833</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1415266</t>
+          <t>1363833</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15993,32 +15993,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2433622</t>
+          <t>2672882</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>1848070</t>
+          <t>2625824</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2659127</t>
+          <t>2718744</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -16028,32 +16028,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>2806345</t>
+          <t>2782065</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2761894</t>
+          <t>2748091</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2873844</t>
+          <t>2814892</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -16063,32 +16063,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>5239968</t>
+          <t>5454948</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>4490991</t>
+          <t>5393247</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5481471</t>
+          <t>5509344</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -16106,32 +16106,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>166193</t>
+          <t>189040</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>126552</t>
+          <t>159160</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>199545</t>
+          <t>220265</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -16141,32 +16141,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>159664</t>
+          <t>178084</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>127200</t>
+          <t>156019</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>186388</t>
+          <t>202712</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -16176,32 +16176,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>325857</t>
+          <t>367125</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>276505</t>
+          <t>331380</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>372829</t>
+          <t>412395</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -16219,32 +16219,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>121117</t>
+          <t>131514</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>85348</t>
+          <t>108909</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>147090</t>
+          <t>159600</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -16254,32 +16254,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>83729</t>
+          <t>94255</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>63787</t>
+          <t>78682</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>100828</t>
+          <t>112553</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -16289,32 +16289,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>204845</t>
+          <t>225769</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>172523</t>
+          <t>199287</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>238420</t>
+          <t>256636</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -16332,32 +16332,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>381516</t>
+          <t>156361</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>138693</t>
+          <t>128852</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1035544</t>
+          <t>191559</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -16367,32 +16367,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>106493</t>
+          <t>117982</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>83290</t>
+          <t>99873</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>128814</t>
+          <t>139077</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -16402,32 +16402,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>488010</t>
+          <t>274343</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>236994</t>
+          <t>241745</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1295377</t>
+          <t>311088</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -16445,17 +16445,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3102448</t>
+          <t>3149798</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3102448</t>
+          <t>3149798</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3102448</t>
+          <t>3149798</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -16480,17 +16480,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3156231</t>
+          <t>3172386</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3156231</t>
+          <t>3172386</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3156231</t>
+          <t>3172386</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -16515,17 +16515,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>6258680</t>
+          <t>6322184</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6258680</t>
+          <t>6322184</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>6258680</t>
+          <t>6322184</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
